--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488258_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488258_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1588</v>
+        <v>6.7268</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4876</v>
+        <v>7.8586</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3288</v>
+        <v>-1.1318</v>
       </c>
       <c r="G2" t="n">
         <v>4.3575</v>
@@ -610,13 +610,13 @@
         <v>1.8529</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7403999999999999</v>
+        <v>0.8276</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6901</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0503</v>
+        <v>0.1467</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1259</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
+          <t>E. PINA FURTADO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6792</v>
+        <v>1.3711</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0328</v>
+        <v>1.645</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6464</v>
+        <v>-0.2739</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.1767</v>
+        <v>-2.611</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.7468</v>
+        <v>0.2936</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4299</v>
+        <v>-2.9046</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.8373</v>
+        <v>-0.227</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.0447</v>
+        <v>1.6486</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2074</v>
+        <v>-1.8756</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3394</v>
+        <v>-2.384</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-1.355</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6373</v>
+        <v>-1.029</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2234</v>
+        <v>-0.9264</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8529</v>
+        <v>1.6676</v>
       </c>
       <c r="S3" t="n">
-        <v>3.9676</v>
+        <v>1.6045</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4647</v>
+        <v>1.2252</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5029</v>
+        <v>0.3793</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2589</v>
+        <v>1.6365</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6289</v>
+        <v>1.5733</v>
       </c>
       <c r="X3" t="n">
-        <v>0.63</v>
+        <v>0.06320000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. PINA FURTADO</t>
+          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7891</v>
+        <v>1.0603</v>
       </c>
       <c r="E4" t="n">
-        <v>1.743</v>
+        <v>-1.0444</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0462</v>
+        <v>2.1047</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.611</v>
+        <v>-2.1767</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2936</v>
+        <v>-1.7468</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.9046</v>
+        <v>-0.4299</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.227</v>
+        <v>-0.8373</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6486</v>
+        <v>-1.0447</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.8756</v>
+        <v>0.2074</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.384</v>
+        <v>-1.3394</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.355</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.029</v>
+        <v>-0.6373</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7411</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9264</v>
+        <v>-2.2234</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6676</v>
+        <v>1.8529</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0225</v>
+        <v>2.3487</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3231</v>
+        <v>1.3875</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6993</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6365</v>
+        <v>1.2589</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5733</v>
+        <v>0.6289</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.129</v>
+        <v>0.7855</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3502</v>
+        <v>2.1544</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2212</v>
+        <v>-1.3689</v>
       </c>
       <c r="G5" t="n">
         <v>1.6555</v>
@@ -844,13 +844,13 @@
         <v>0.3706</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8615</v>
+        <v>0.5179</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5434</v>
+        <v>0.3476</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3181</v>
+        <v>0.1704</v>
       </c>
       <c r="V5" t="n">
         <v>-1.5733</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. BRAVO ORTEGA</t>
+          <t>Á. LLAMAS JIMENEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6784</v>
+        <v>0.6221</v>
       </c>
       <c r="E6" t="n">
-        <v>5.0272</v>
+        <v>0.6221</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.3488</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0392</v>
+        <v>0.6221</v>
       </c>
       <c r="H6" t="n">
-        <v>1.904</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8647</v>
+        <v>0.6221</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4195</v>
+        <v>0.6221</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4088</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0107</v>
+        <v>0.6221</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3803</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5048</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8754</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4.2969</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.5342</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7628</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-4.6578</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-4.6578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Á. LLAMAS JIMENEZ</t>
+          <t>O. KANTE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6221</v>
+        <v>-1.5603</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6221</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-0.8249</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6221</v>
+        <v>-1.5511</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-2.1686</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6221</v>
+        <v>0.6175</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6221</v>
+        <v>-0.128</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-1.5593</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6221</v>
+        <v>1.4314</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-1.4231</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.8138</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.297</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.0382</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.3897</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.6896</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.14</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. KANTE</t>
+          <t>M. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8076</v>
+        <v>-1.992</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5395</v>
+        <v>2.6769</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2681</v>
+        <v>-4.6689</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5511</v>
+        <v>1.0392</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.1686</v>
+        <v>1.904</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6175</v>
+        <v>-0.8647</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.128</v>
+        <v>2.4195</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.5593</v>
+        <v>2.4088</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4314</v>
+        <v>0.0107</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4231</v>
+        <v>-1.3803</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6093</v>
+        <v>-0.5048</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8138</v>
+        <v>-0.8754</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.297</v>
+        <v>-0.9264</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0382</v>
+        <v>0.9264</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1423</v>
+        <v>1.6265</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8854</v>
+        <v>1.1839</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2569</v>
+        <v>0.4427</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.14</v>
+        <v>-4.6578</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.14</v>
+        <v>-4.6578</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Y. VAQUERO HERNANDEZ</t>
+          <t>F. BENITEZ SIERRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4567</v>
+        <v>-2.3636</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4781</v>
+        <v>-1.3561</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0214</v>
+        <v>-1.0075</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6652</v>
+        <v>-0.8669</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.315</v>
+        <v>-0.0145</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3502</v>
+        <v>-0.8524</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.114</v>
+        <v>0.1074</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5026</v>
+        <v>0.1074</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5513</v>
+        <v>-0.9743000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8124</v>
+        <v>-0.1219</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2611</v>
+        <v>-0.8524</v>
       </c>
       <c r="P9" t="n">
         <v>-1.4823</v>
@@ -1156,28 +1156,28 @@
         <v>0.3706</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5011</v>
+        <v>0.3</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4887</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0124</v>
+        <v>0.2251</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1897</v>
+        <v>-0.3144</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1897</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. BENITEZ SIERRA</t>
+          <t>Y. VAQUERO HERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7067</v>
+        <v>-2.6526</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6499</v>
+        <v>-2.674</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0567</v>
+        <v>0.0214</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8669</v>
+        <v>-1.6652</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0145</v>
+        <v>-1.315</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8524</v>
+        <v>-0.3502</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1074</v>
+        <v>-1.114</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1074</v>
+        <v>-0.5026</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-0.5513</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1219</v>
+        <v>-0.8124</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8524</v>
+        <v>0.2611</v>
       </c>
       <c r="P10" t="n">
         <v>-1.4823</v>
@@ -1234,22 +1234,22 @@
         <v>0.3706</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.043</v>
+        <v>0.3053</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2189</v>
+        <v>0.2929</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1758</v>
+        <v>0.0124</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3144</v>
+        <v>0.1897</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6289</v>
+        <v>0.1897</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.133</v>
+        <v>-3.4224</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3265</v>
+        <v>-3.739</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1935</v>
+        <v>0.3166</v>
       </c>
       <c r="G11" t="n">
         <v>0.45</v>
@@ -1312,13 +1312,13 @@
         <v>1.1117</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4402</v>
+        <v>0.2705</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8754</v>
+        <v>-0.2879</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4352</v>
+        <v>0.5583</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2518</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3196</v>
+        <v>-3.6816</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8166</v>
+        <v>-2.4249</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.503</v>
+        <v>-1.2568</v>
       </c>
       <c r="G12" t="n">
         <v>0.6943</v>
@@ -1390,13 +1390,13 @@
         <v>1.297</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4129</v>
+        <v>1.0508</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1057</v>
+        <v>0.4974</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3071</v>
+        <v>0.5534</v>
       </c>
       <c r="V12" t="n">
         <v>-2.8327</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.7032</v>
+        <v>-3.9634</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.6177</v>
+        <v>-2.1487</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0855</v>
+        <v>-1.8147</v>
       </c>
       <c r="G13" t="n">
         <v>-2.9912</v>
@@ -1468,13 +1468,13 @@
         <v>2.0382</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2112</v>
+        <v>1.5286</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6901</v>
+        <v>0.7788</v>
       </c>
       <c r="U13" t="n">
-        <v>0.479</v>
+        <v>0.7498</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5744</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.0702</v>
+        <v>-9.0701</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8345999999999991</v>
+        <v>0.8345000000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.9046</v>
+        <v>-9.9047</v>
       </c>
       <c r="G14" t="n">
         <v>-3.0435</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8714</v>
+        <v>1.871400000000001</v>
       </c>
       <c r="I14" t="n">
         <v>-4.9148</v>
@@ -1525,7 +1525,7 @@
         <v>7.9062</v>
       </c>
       <c r="L14" t="n">
-        <v>2.6485</v>
+        <v>2.648500000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-13.5984</v>
@@ -1537,7 +1537,7 @@
         <v>-7.5634</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.4115</v>
+        <v>-7.411499999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>-21.3079</v>
@@ -1546,13 +1546,13 @@
         <v>13.8967</v>
       </c>
       <c r="S14" t="n">
-        <v>11.77</v>
+        <v>11.7701</v>
       </c>
       <c r="T14" t="n">
-        <v>6.870699999999998</v>
+        <v>6.870800000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>4.8992</v>
+        <v>4.8994</v>
       </c>
       <c r="V14" t="n">
         <v>-10.3852</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.589399999999999</v>
+        <v>9.892899999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>9.245200000000001</v>
+        <v>9.1473</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3442</v>
+        <v>0.7456</v>
       </c>
       <c r="G15" t="n">
         <v>4.6834</v>
@@ -1624,13 +1624,13 @@
         <v>3.1499</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.0553</v>
+        <v>-1.7518</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8244</v>
+        <v>-0.9224</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.2309</v>
+        <v>-0.8295</v>
       </c>
       <c r="V15" t="n">
         <v>5.6643</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.9397</v>
+        <v>7.607</v>
       </c>
       <c r="E16" t="n">
-        <v>6.7595</v>
+        <v>5.976</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1803</v>
+        <v>1.6309</v>
       </c>
       <c r="G16" t="n">
         <v>5.6942</v>
@@ -1702,13 +1702,13 @@
         <v>2.4087</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7926</v>
+        <v>-1.1254</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1567</v>
+        <v>-0.6267</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9493</v>
+        <v>-0.4987</v>
       </c>
       <c r="V16" t="n">
         <v>0.6294</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.7021</v>
+        <v>2.0431</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3111</v>
+        <v>1.9401</v>
       </c>
       <c r="F17" t="n">
-        <v>0.391</v>
+        <v>0.103</v>
       </c>
       <c r="G17" t="n">
         <v>-1.3712</v>
@@ -1780,13 +1780,13 @@
         <v>2.594</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8874</v>
+        <v>-0.7716</v>
       </c>
       <c r="T17" t="n">
-        <v>1.353</v>
+        <v>-0.018</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4656</v>
+        <v>-0.7536</v>
       </c>
       <c r="V17" t="n">
         <v>2.5183</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4542</v>
+        <v>-0.1867</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1214</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6672</v>
+        <v>0.3471</v>
       </c>
       <c r="G19" t="n">
         <v>1.1449</v>
@@ -1936,13 +1936,13 @@
         <v>2.9646</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.452</v>
+        <v>-1.1845</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3132</v>
+        <v>-0.7256</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1388</v>
+        <v>-0.4589</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2589</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6249</v>
+        <v>-0.5939</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8501</v>
+        <v>-0.6542</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2252</v>
+        <v>0.0603</v>
       </c>
       <c r="G20" t="n">
         <v>2.7747</v>
@@ -2014,13 +2014,13 @@
         <v>1.8529</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2503</v>
+        <v>-1.2193</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9849</v>
+        <v>-0.789</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2654</v>
+        <v>-0.4303</v>
       </c>
       <c r="V20" t="n">
         <v>0.63</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3066</v>
+        <v>-1.4241</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2962</v>
+        <v>-0.6107</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0103</v>
+        <v>-0.8134</v>
       </c>
       <c r="G21" t="n">
         <v>-3.184</v>
@@ -2092,13 +2092,13 @@
         <v>2.9646</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.1046</v>
+        <v>-1.2221</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2037</v>
+        <v>-0.5182</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9008</v>
+        <v>-0.7039</v>
       </c>
       <c r="V21" t="n">
         <v>0.9439</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. MARTINEZ AGUDO</t>
+          <t>J. LOPEZ YUSTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9684</v>
+        <v>-2.4887</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6338</v>
+        <v>-3.5664</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3346</v>
+        <v>1.0777</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.5892</v>
+        <v>-1.2422</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.3804</v>
+        <v>-2.0056</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2088</v>
+        <v>0.7633</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.4921</v>
+        <v>-0.4164</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3523</v>
+        <v>-1.817</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1398</v>
+        <v>1.4006</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0971</v>
+        <v>-0.8258</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.0281</v>
+        <v>-0.1885</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.6373</v>
       </c>
       <c r="P22" t="n">
-        <v>2.7793</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-3.7057</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7793</v>
+        <v>2.2234</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.1585</v>
+        <v>-1.338</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.715</v>
+        <v>-0.7026</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.4435</v>
+        <v>-0.6355</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.5738</v>
       </c>
       <c r="W22" t="n">
-        <v>1.5733</v>
+        <v>1.2583</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.5733</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B. ARIAS HERNANDEZ</t>
+          <t>A. MARTINEZ AGUDO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0441</v>
+        <v>-2.6248</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8734</v>
+        <v>-0.438</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1707</v>
+        <v>-2.1869</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.1891</v>
+        <v>-3.5892</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.7514</v>
+        <v>-2.3804</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4377</v>
+        <v>-1.2088</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2843</v>
+        <v>-1.4921</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2843</v>
+        <v>-0.3523</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-1.1398</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9048</v>
+        <v>-2.0971</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4671</v>
+        <v>-2.0281</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4377</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3706</v>
+        <v>2.7793</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3706</v>
+        <v>2.7793</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.91</v>
+        <v>-1.8149</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2736</v>
+        <v>-0.5192</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6364</v>
+        <v>-1.2958</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3155</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3155</v>
+        <v>1.5733</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. LOPEZ YUSTE</t>
+          <t>B. ARIAS HERNANDEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0849</v>
+        <v>-2.8236</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.9581</v>
+        <v>-1.6775</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8733</v>
+        <v>-1.1461</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.2422</v>
+        <v>-2.1891</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.0056</v>
+        <v>-1.7514</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7633</v>
+        <v>-0.4377</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4164</v>
+        <v>-1.2843</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.817</v>
+        <v>-1.2843</v>
       </c>
       <c r="L24" t="n">
-        <v>1.4006</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8258</v>
+        <v>-0.9048</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1885</v>
+        <v>-0.4671</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6373</v>
+        <v>-0.4377</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.4823</v>
+        <v>0.3706</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.7057</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.2234</v>
+        <v>0.3706</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.9342</v>
+        <v>-0.6895</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0943</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8399</v>
+        <v>-0.6118</v>
       </c>
       <c r="V24" t="n">
-        <v>1.5738</v>
+        <v>-0.3155</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2583</v>
+        <v>-0.3155</v>
       </c>
       <c r="X24" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,28 +2359,28 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>9.0702</v>
+        <v>9.723299999999998</v>
       </c>
       <c r="E25" t="n">
-        <v>9.904899999999998</v>
+        <v>9.9049</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8343999999999998</v>
+        <v>-0.1817999999999997</v>
       </c>
       <c r="G25" t="n">
-        <v>3.043600000000002</v>
+        <v>3.043600000000003</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.8715</v>
+        <v>-1.871500000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>4.915</v>
+        <v>4.914999999999999</v>
       </c>
       <c r="J25" t="n">
         <v>13.5982</v>
       </c>
       <c r="K25" t="n">
-        <v>6.034700000000001</v>
+        <v>6.034700000000002</v>
       </c>
       <c r="L25" t="n">
         <v>7.5635</v>
@@ -2389,13 +2389,13 @@
         <v>-10.5545</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.906100000000001</v>
+        <v>-7.9061</v>
       </c>
       <c r="O25" t="n">
         <v>-2.6485</v>
       </c>
       <c r="P25" t="n">
-        <v>7.411499999999998</v>
+        <v>7.411499999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-13.8965</v>
@@ -2404,13 +2404,13 @@
         <v>21.308</v>
       </c>
       <c r="S25" t="n">
-        <v>-11.7701</v>
+        <v>-11.1171</v>
       </c>
       <c r="T25" t="n">
         <v>-4.8994</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.8706</v>
+        <v>-6.218</v>
       </c>
       <c r="V25" t="n">
         <v>10.3853</v>
